--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -435,25 +435,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2">
-        <v>31.91</v>
+        <v>37.14</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G2">
-        <v>92.2</v>
+        <v>95.27</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -476,10 +476,10 @@
         <v>6</v>
       </c>
       <c r="G3">
-        <v>43.04</v>
+        <v>46.68</v>
       </c>
       <c r="H3">
-        <v>56.96</v>
+        <v>53.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>37.14</v>
+        <v>37.7</v>
       </c>
       <c r="D2">
         <v>33</v>
@@ -450,10 +450,10 @@
         <v>87</v>
       </c>
       <c r="G2">
-        <v>95.27</v>
+        <v>95.48</v>
       </c>
       <c r="H2">
-        <v>4.73</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -435,25 +435,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>37.7</v>
+        <v>43.64</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="F2">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="G2">
-        <v>95.48</v>
+        <v>92.5</v>
       </c>
       <c r="H2">
-        <v>4.52</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -461,25 +461,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0.45</v>
+        <v>3.7</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>46.68</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="H3">
-        <v>53.32</v>
+        <v>28.04</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>43.64</v>
+        <v>43.65</v>
       </c>
       <c r="D2">
         <v>39</v>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>43.65</v>
+        <v>43.64</v>
       </c>
       <c r="D2">
         <v>39</v>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>43.65</v>
+        <v>43.66</v>
       </c>
       <c r="D2">
         <v>39</v>
@@ -450,10 +450,10 @@
         <v>111</v>
       </c>
       <c r="G2">
-        <v>92.5</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -435,25 +435,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2">
-        <v>43.66</v>
+        <v>46.55</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="F2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G2">
-        <v>92.48999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="H2">
-        <v>7.51</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>3.89</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -476,10 +476,10 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>71.95999999999999</v>
+        <v>74.08</v>
       </c>
       <c r="H3">
-        <v>28.04</v>
+        <v>25.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,22 +438,22 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>46.55</v>
+        <v>45.25</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="F2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G2">
-        <v>93.45</v>
+        <v>93.02</v>
       </c>
       <c r="H2">
-        <v>6.55</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -476,10 +476,10 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>74.08</v>
+        <v>74.86</v>
       </c>
       <c r="H3">
-        <v>25.92</v>
+        <v>25.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,22 +438,22 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>45.25</v>
+        <v>46.3</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="F2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G2">
-        <v>93.02</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H2">
-        <v>6.98</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -438,22 +438,22 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>46.3</v>
+        <v>49.19</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E2">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="F2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G2">
-        <v>93.26000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="H2">
-        <v>6.74</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>4.04</v>
+        <v>4.25</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -476,10 +476,10 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>74.86</v>
+        <v>75.44</v>
       </c>
       <c r="H3">
-        <v>25.14</v>
+        <v>24.56</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -476,10 +476,10 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>75.44</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="H3">
-        <v>24.56</v>
+        <v>24.01</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -435,13 +435,13 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C2">
-        <v>49.19</v>
+        <v>51.16</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -450,10 +450,10 @@
         <v>119</v>
       </c>
       <c r="G2">
-        <v>94.13</v>
+        <v>94.98</v>
       </c>
       <c r="H2">
-        <v>5.87</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,22 +464,22 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>4.34</v>
+        <v>2.83</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>75.98999999999999</v>
+        <v>65.37</v>
       </c>
       <c r="H3">
-        <v>24.01</v>
+        <v>34.63</v>
       </c>
     </row>
   </sheetData>
